--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Documents\ฝึกสร้างเว็บ\Daily_DC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Desktop\ฝึกสร้างเว็บ\Daily_DC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -1057,6 +1057,9 @@
   <si>
     <t>time pi datalink</t>
   </si>
+  <si>
+    <t>ENA</t>
+  </si>
 </sst>
 </file>
 
@@ -1246,6 +1249,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1336,7 +1340,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000025-06C4-4EBD-9DB5-5F6028942F55}"/>
                 </c:ext>
@@ -1358,7 +1364,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1659,6 +1667,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1667,7 +1676,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1675,6 +1686,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1683,7 +1695,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -2101,6 +2115,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5435,7 +5450,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5500,7 +5514,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5509,9 +5522,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000008-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5519,7 +5530,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5528,9 +5538,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5830,7 +5838,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5839,9 +5846,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -6259,7 +6264,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7302,7 +7306,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7367,7 +7370,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7376,9 +7378,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-E73E-4A56-8161-D7588DDD0A4F}"/>
                 </c:ext>
@@ -7386,7 +7386,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7395,9 +7394,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -7697,7 +7694,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7706,9 +7702,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -8126,7 +8120,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -19264,43 +19257,141 @@
       <c r="C60" s="13">
         <v>46081</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
-      <c r="AB60" s="4"/>
-      <c r="AC60" s="4"/>
-      <c r="AD60" s="4"/>
-      <c r="AE60" s="4"/>
-      <c r="AF60" s="4"/>
-      <c r="AG60" s="4"/>
-      <c r="AH60" s="4"/>
-      <c r="AI60" s="4"/>
-      <c r="AJ60" s="4"/>
-      <c r="AK60" s="4"/>
-      <c r="AL60" s="4"/>
-      <c r="AM60" s="4"/>
-      <c r="AN60" s="4"/>
+      <c r="D60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C60,0,"","auto")</f>
+        <v>212.24351501464844</v>
+      </c>
+      <c r="E60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C60,0,"","auto")</f>
+        <v>556.39813232421875</v>
+      </c>
+      <c r="F60" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C60,0,"","auto")</f>
+        <v>402737.375</v>
+      </c>
+      <c r="G60" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C60,0,"","auto")</f>
+        <v>137431.109375</v>
+      </c>
+      <c r="H60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C60,0,"","auto")</f>
+        <v>45.089576721191406</v>
+      </c>
+      <c r="I60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C60,0,"","auto")</f>
+        <v>52.010173797607422</v>
+      </c>
+      <c r="J60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C60,0,"","auto")</f>
+        <v>63181.3984375</v>
+      </c>
+      <c r="K60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C60,0,"","auto")</f>
+        <v>191051.296875</v>
+      </c>
+      <c r="L60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C60,0,"","auto")</f>
+        <v>1445.300048828125</v>
+      </c>
+      <c r="M60" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C60,0,"","auto")</f>
+        <v>1619.1600341796875</v>
+      </c>
+      <c r="N60" s="8">
+        <f t="shared" ref="N60:N65" si="42">(J60+F60-F59)/(D60*H60/100)/1000</f>
+        <v>0.64139983520790045</v>
+      </c>
+      <c r="O60" s="8">
+        <f t="shared" ref="O60:O65" si="43">(K60+G60-G59)/(E60*I60/100)/1000</f>
+        <v>0.64140602092753762</v>
+      </c>
+      <c r="P60" s="8">
+        <f t="shared" ref="P60:P65" si="44">((J60+K60)+F60+G60-F59-G59)/(D60*H60/100+E60*I60/100)/1000</f>
+        <v>0.6414044836719085</v>
+      </c>
+      <c r="Q60" s="8">
+        <f t="shared" ref="Q60:Q65" si="45">P60*H60*10</f>
+        <v>289.20656675840678</v>
+      </c>
+      <c r="R60" s="8">
+        <f t="shared" ref="R60:R65" si="46">P60*I60*10</f>
+        <v>333.59558670340613</v>
+      </c>
+      <c r="S60" s="4">
+        <f t="shared" ref="S60:S65" si="47">((J60+K60)+F60+G60-F59-G59)/(D60+E60)</f>
+        <v>321.33853342793032</v>
+      </c>
+      <c r="T60" s="5">
+        <f t="shared" ref="T60:T65" si="48">IF(AL60&lt;3000,0,AL60)</f>
+        <v>255213.796875</v>
+      </c>
+      <c r="U60" s="5">
+        <f t="shared" ref="U60:U65" si="49">IF(AM60&lt;3000,0,AM60)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="5">
+        <f t="shared" ref="V60:V65" si="50">IF(AN60&lt;3000,0,AN60)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="X60" s="7">
+        <f t="shared" ref="X60:X65" si="51">J60+K60</f>
+        <v>254232.6953125</v>
+      </c>
+      <c r="Y60" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z60" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA60" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB60" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC60" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD60" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE60" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF60" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG60" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH60" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="4">
+        <f t="shared" ref="AK60:AK65" si="52">SUM(AH60:AJ60)</f>
+        <v>252143</v>
+      </c>
+      <c r="AL60" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C60,0,"","auto")</f>
+        <v>255213.796875</v>
+      </c>
+      <c r="AM60" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C60,0,"","auto")</f>
+        <v>-936.77105712890625</v>
+      </c>
+      <c r="AN60" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C60,0,"","auto")</f>
+        <v>12.999432563781738</v>
+      </c>
     </row>
     <row r="61" spans="2:40">
       <c r="B61" s="20">
@@ -19309,43 +19400,140 @@
       <c r="C61" s="13">
         <v>46082</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
-      <c r="AB61" s="4"/>
-      <c r="AC61" s="4"/>
-      <c r="AD61" s="4"/>
-      <c r="AE61" s="4"/>
-      <c r="AF61" s="4"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="4"/>
-      <c r="AI61" s="4"/>
-      <c r="AJ61" s="4"/>
-      <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
-      <c r="AM61" s="4"/>
-      <c r="AN61" s="4"/>
+      <c r="D61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C61,0,"","auto")</f>
+        <v>202.87850952148438</v>
+      </c>
+      <c r="E61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C61,0,"","auto")</f>
+        <v>524.84716796875</v>
+      </c>
+      <c r="F61" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C61,0,"","auto")</f>
+        <v>401849.71875</v>
+      </c>
+      <c r="G61" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C61,0,"","auto")</f>
+        <v>134733.75</v>
+      </c>
+      <c r="H61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C61,0,"","auto")</f>
+        <v>44.480117797851563</v>
+      </c>
+      <c r="I61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C61,0,"","auto")</f>
+        <v>52.259498596191406</v>
+      </c>
+      <c r="J61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C61,0,"","auto")</f>
+        <v>42158.80859375</v>
+      </c>
+      <c r="K61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C61,0,"","auto")</f>
+        <v>128138.7109375</v>
+      </c>
+      <c r="L61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C61,0,"","auto")</f>
+        <v>1445.038818359375</v>
+      </c>
+      <c r="M61" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C61,0,"","auto")</f>
+        <v>1618.8096923828125</v>
+      </c>
+      <c r="N61" s="8">
+        <f t="shared" si="42"/>
+        <v>0.45734572170213794</v>
+      </c>
+      <c r="O61" s="8">
+        <f t="shared" si="43"/>
+        <v>0.45734362310708726</v>
+      </c>
+      <c r="P61" s="8">
+        <f t="shared" si="44"/>
+        <v>0.45734414263102796</v>
+      </c>
+      <c r="Q61" s="8">
+        <f t="shared" si="45"/>
+        <v>203.42721338385553</v>
+      </c>
+      <c r="R61" s="8">
+        <f t="shared" si="46"/>
+        <v>239.00575579802566</v>
+      </c>
+      <c r="S61" s="4">
+        <f t="shared" si="47"/>
+        <v>229.08701597723569</v>
+      </c>
+      <c r="T61" s="5">
+        <f t="shared" si="48"/>
+        <v>65124.890625</v>
+      </c>
+      <c r="U61" s="5">
+        <f t="shared" si="49"/>
+        <v>105240.5625</v>
+      </c>
+      <c r="V61" s="5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="W61" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X61" s="7">
+        <f t="shared" si="51"/>
+        <v>170297.51953125</v>
+      </c>
+      <c r="Y61" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z61" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA61" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB61" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC61" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD61" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE61" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF61" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG61" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH61" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="4">
+        <v>100000</v>
+      </c>
+      <c r="AL61" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C61,0,"","auto")</f>
+        <v>65124.890625</v>
+      </c>
+      <c r="AM61" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C61,0,"","auto")</f>
+        <v>105240.5625</v>
+      </c>
+      <c r="AN61" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C61,0,"","auto")</f>
+        <v>-35.998703002929688</v>
+      </c>
     </row>
     <row r="62" spans="2:40">
       <c r="B62" s="20">
@@ -19354,43 +19542,140 @@
       <c r="C62" s="13">
         <v>46083</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
-      <c r="AB62" s="4"/>
-      <c r="AC62" s="4"/>
-      <c r="AD62" s="4"/>
-      <c r="AE62" s="4"/>
-      <c r="AF62" s="4"/>
-      <c r="AG62" s="4"/>
-      <c r="AH62" s="4"/>
-      <c r="AI62" s="4"/>
-      <c r="AJ62" s="4"/>
-      <c r="AK62" s="4"/>
-      <c r="AL62" s="4"/>
-      <c r="AM62" s="4"/>
-      <c r="AN62" s="4"/>
+      <c r="D62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C62,0,"","auto")</f>
+        <v>143.21257019042969</v>
+      </c>
+      <c r="E62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C62,0,"","auto")</f>
+        <v>405.64373779296875</v>
+      </c>
+      <c r="F62" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C62,0,"","auto")</f>
+        <v>415831.125</v>
+      </c>
+      <c r="G62" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C62,0,"","auto")</f>
+        <v>180450.515625</v>
+      </c>
+      <c r="H62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C62,0,"","auto")</f>
+        <v>44.650215148925781</v>
+      </c>
+      <c r="I62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C62,0,"","auto")</f>
+        <v>51.540210723876953</v>
+      </c>
+      <c r="J62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C62,0,"","auto")</f>
+        <v>28945.197265625</v>
+      </c>
+      <c r="K62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C62,0,"","auto")</f>
+        <v>94633.5703125</v>
+      </c>
+      <c r="L62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C62,0,"","auto")</f>
+        <v>1069.0787353515625</v>
+      </c>
+      <c r="M62" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C62,0,"","auto")</f>
+        <v>1115.1427001953125</v>
+      </c>
+      <c r="N62" s="8">
+        <f t="shared" si="42"/>
+        <v>0.67130801477858737</v>
+      </c>
+      <c r="O62" s="8">
+        <f t="shared" si="43"/>
+        <v>0.67130903265443265</v>
+      </c>
+      <c r="P62" s="8">
+        <f t="shared" si="44"/>
+        <v>0.67130879425017032</v>
+      </c>
+      <c r="Q62" s="8">
+        <f t="shared" si="45"/>
+        <v>299.74082094636054</v>
+      </c>
+      <c r="R62" s="8">
+        <f t="shared" si="46"/>
+        <v>345.99396716445534</v>
+      </c>
+      <c r="S62" s="4">
+        <f t="shared" si="47"/>
+        <v>333.92517638454228</v>
+      </c>
+      <c r="T62" s="5">
+        <f t="shared" si="48"/>
+        <v>55842.078125</v>
+      </c>
+      <c r="U62" s="5">
+        <f t="shared" si="49"/>
+        <v>67640.265625</v>
+      </c>
+      <c r="V62" s="5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X62" s="7">
+        <f t="shared" si="51"/>
+        <v>123578.767578125</v>
+      </c>
+      <c r="Y62" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD62" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE62" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF62" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG62" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH62" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL62" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C62,0,"","auto")</f>
+        <v>55842.078125</v>
+      </c>
+      <c r="AM62" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C62,0,"","auto")</f>
+        <v>67640.265625</v>
+      </c>
+      <c r="AN62" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C62,0,"","auto")</f>
+        <v>76.001998901367188</v>
+      </c>
     </row>
     <row r="63" spans="2:40">
       <c r="B63" s="20">
@@ -19399,43 +19684,140 @@
       <c r="C63" s="13">
         <v>46084</v>
       </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
-      <c r="AB63" s="4"/>
-      <c r="AC63" s="4"/>
-      <c r="AD63" s="4"/>
-      <c r="AE63" s="4"/>
-      <c r="AF63" s="4"/>
-      <c r="AG63" s="4"/>
-      <c r="AH63" s="4"/>
-      <c r="AI63" s="4"/>
-      <c r="AJ63" s="4"/>
-      <c r="AK63" s="4"/>
-      <c r="AL63" s="4"/>
-      <c r="AM63" s="4"/>
-      <c r="AN63" s="4"/>
+      <c r="D63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C63,0,"","auto")</f>
+        <v>190.10929870605469</v>
+      </c>
+      <c r="E63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C63,0,"","auto")</f>
+        <v>396.69876098632813</v>
+      </c>
+      <c r="F63" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C63,0,"","auto")</f>
+        <v>427506.09375</v>
+      </c>
+      <c r="G63" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C63,0,"","auto")</f>
+        <v>208538.140625</v>
+      </c>
+      <c r="H63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C63,0,"","auto")</f>
+        <v>44.959903717041016</v>
+      </c>
+      <c r="I63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C63,0,"","auto")</f>
+        <v>51.839824676513672</v>
+      </c>
+      <c r="J63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C63,0,"","auto")</f>
+        <v>45063.12109375</v>
+      </c>
+      <c r="K63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C63,0,"","auto")</f>
+        <v>108421.875</v>
+      </c>
+      <c r="L63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C63,0,"","auto")</f>
+        <v>1038.6761474609375</v>
+      </c>
+      <c r="M63" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C63,0,"","auto")</f>
+        <v>1809.328369140625</v>
+      </c>
+      <c r="N63" s="8">
+        <f t="shared" si="42"/>
+        <v>0.66381334401122094</v>
+      </c>
+      <c r="O63" s="8">
+        <f t="shared" si="43"/>
+        <v>0.66380192549847661</v>
+      </c>
+      <c r="P63" s="8">
+        <f t="shared" si="44"/>
+        <v>0.6638052779683844</v>
+      </c>
+      <c r="Q63" s="8">
+        <f t="shared" si="45"/>
+        <v>298.4462138432221</v>
+      </c>
+      <c r="R63" s="8">
+        <f t="shared" si="46"/>
+        <v>344.11549229225471</v>
+      </c>
+      <c r="S63" s="4">
+        <f t="shared" si="47"/>
+        <v>329.31993119701605</v>
+      </c>
+      <c r="T63" s="5">
+        <f t="shared" si="48"/>
+        <v>62621.4921875</v>
+      </c>
+      <c r="U63" s="5">
+        <f t="shared" si="49"/>
+        <v>90588.9453125</v>
+      </c>
+      <c r="V63" s="5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="W63" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X63" s="7">
+        <f t="shared" si="51"/>
+        <v>153484.99609375</v>
+      </c>
+      <c r="Y63" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z63" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA63" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB63" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC63" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD63" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE63" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF63" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG63" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH63" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI63" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL63" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C63,0,"","auto")</f>
+        <v>62621.4921875</v>
+      </c>
+      <c r="AM63" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C63,0,"","auto")</f>
+        <v>90588.9453125</v>
+      </c>
+      <c r="AN63" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C63,0,"","auto")</f>
+        <v>248.99681091308594</v>
+      </c>
     </row>
     <row r="64" spans="2:40">
       <c r="B64" s="20">
@@ -19444,43 +19826,140 @@
       <c r="C64" s="13">
         <v>46085</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
-      <c r="AB64" s="4"/>
-      <c r="AC64" s="4"/>
-      <c r="AD64" s="4"/>
-      <c r="AE64" s="4"/>
-      <c r="AF64" s="4"/>
-      <c r="AG64" s="4"/>
-      <c r="AH64" s="4"/>
-      <c r="AI64" s="4"/>
-      <c r="AJ64" s="4"/>
-      <c r="AK64" s="4"/>
-      <c r="AL64" s="4"/>
-      <c r="AM64" s="4"/>
-      <c r="AN64" s="4"/>
+      <c r="D64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C64,0,"","auto")</f>
+        <v>203.48477172851563</v>
+      </c>
+      <c r="E64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C64,0,"","auto")</f>
+        <v>466.8055419921875</v>
+      </c>
+      <c r="F64" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C64,0,"","auto")</f>
+        <v>431948.90625</v>
+      </c>
+      <c r="G64" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C64,0,"","auto")</f>
+        <v>220270.015625</v>
+      </c>
+      <c r="H64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C64,0,"","auto")</f>
+        <v>44.819778442382813</v>
+      </c>
+      <c r="I64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C64,0,"","auto")</f>
+        <v>51.589736938476563</v>
+      </c>
+      <c r="J64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C64,0,"","auto")</f>
+        <v>52429.515625</v>
+      </c>
+      <c r="K64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C64,0,"","auto")</f>
+        <v>138443.359375</v>
+      </c>
+      <c r="L64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C64,0,"","auto")</f>
+        <v>1148.2994384765625</v>
+      </c>
+      <c r="M64" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C64,0,"","auto")</f>
+        <v>1390.2655029296875</v>
+      </c>
+      <c r="N64" s="8">
+        <f t="shared" si="42"/>
+        <v>0.62359035333537305</v>
+      </c>
+      <c r="O64" s="8">
+        <f t="shared" si="43"/>
+        <v>0.62358979823041194</v>
+      </c>
+      <c r="P64" s="8">
+        <f t="shared" si="44"/>
+        <v>0.62358995070789447</v>
+      </c>
+      <c r="Q64" s="8">
+        <f t="shared" si="45"/>
+        <v>279.49163429624252</v>
+      </c>
+      <c r="R64" s="8">
+        <f t="shared" si="46"/>
+        <v>321.70841514497846</v>
+      </c>
+      <c r="S64" s="4">
+        <f t="shared" si="47"/>
+        <v>308.8923683690179</v>
+      </c>
+      <c r="T64" s="5">
+        <f t="shared" si="48"/>
+        <v>18867</v>
+      </c>
+      <c r="U64" s="5">
+        <f t="shared" si="49"/>
+        <v>172056</v>
+      </c>
+      <c r="V64" s="5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X64" s="7">
+        <f t="shared" si="51"/>
+        <v>190872.875</v>
+      </c>
+      <c r="Y64" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z64" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA64" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB64" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC64" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD64" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE64" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF64" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG64" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH64" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL64" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C64,0,"","auto")</f>
+        <v>18867</v>
+      </c>
+      <c r="AM64" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C64,0,"","auto")</f>
+        <v>172056</v>
+      </c>
+      <c r="AN64" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C64,0,"","auto")</f>
+        <v>-27</v>
+      </c>
     </row>
     <row r="65" spans="2:40">
       <c r="B65" s="20">
@@ -19489,43 +19968,140 @@
       <c r="C65" s="13">
         <v>46086</v>
       </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="4"/>
-      <c r="AE65" s="4"/>
-      <c r="AF65" s="4"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="4"/>
-      <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
-      <c r="AM65" s="4"/>
-      <c r="AN65" s="4"/>
+      <c r="D65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C65,0,"","auto")</f>
+        <v>210.35000610351563</v>
+      </c>
+      <c r="E65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C65,0,"","auto")</f>
+        <v>374.05999755859375</v>
+      </c>
+      <c r="F65" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C65,0,"","auto")</f>
+        <v>437588</v>
+      </c>
+      <c r="G65" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C65,0,"","auto")</f>
+        <v>231812</v>
+      </c>
+      <c r="H65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C65,0,"","auto")</f>
+        <v>44.5</v>
+      </c>
+      <c r="I65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C65,0,"","auto")</f>
+        <v>51.209999084472656</v>
+      </c>
+      <c r="J65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C65,0,"","auto")</f>
+        <v>51730</v>
+      </c>
+      <c r="K65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C65,0,"","auto")</f>
+        <v>105861</v>
+      </c>
+      <c r="L65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C65,0,"","auto")</f>
+        <v>1147.4000244140625</v>
+      </c>
+      <c r="M65" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C65,0,"","auto")</f>
+        <v>2204.159912109375</v>
+      </c>
+      <c r="N65" s="8">
+        <f t="shared" si="42"/>
+        <v>0.61288000027112022</v>
+      </c>
+      <c r="O65" s="8">
+        <f t="shared" si="43"/>
+        <v>0.61289079964053028</v>
+      </c>
+      <c r="P65" s="8">
+        <f t="shared" si="44"/>
+        <v>0.61288725469573047</v>
+      </c>
+      <c r="Q65" s="8">
+        <f t="shared" si="45"/>
+        <v>272.73482833960009</v>
+      </c>
+      <c r="R65" s="8">
+        <f t="shared" si="46"/>
+        <v>313.85955751853317</v>
+      </c>
+      <c r="S65" s="4">
+        <f t="shared" si="47"/>
+        <v>299.05730057634099</v>
+      </c>
+      <c r="T65" s="5">
+        <f t="shared" si="48"/>
+        <v>18867</v>
+      </c>
+      <c r="U65" s="5">
+        <f t="shared" si="49"/>
+        <v>172056</v>
+      </c>
+      <c r="V65" s="5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="W65" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X65" s="7">
+        <f t="shared" si="51"/>
+        <v>157591</v>
+      </c>
+      <c r="Y65" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z65" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA65" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB65" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC65" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD65" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE65" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF65" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG65" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH65" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI65" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL65" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C65,0,"","auto")</f>
+        <v>18867</v>
+      </c>
+      <c r="AM65" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C65,0,"","auto")</f>
+        <v>172056</v>
+      </c>
+      <c r="AN65" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C65,0,"","auto")</f>
+        <v>-27</v>
+      </c>
     </row>
     <row r="66" spans="2:40">
       <c r="B66" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -1249,7 +1249,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1340,9 +1339,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000025-06C4-4EBD-9DB5-5F6028942F55}"/>
                 </c:ext>
@@ -1364,9 +1361,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1667,7 +1662,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1676,9 +1670,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1686,7 +1678,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1695,9 +1686,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -2115,7 +2104,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -19377,7 +19365,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="4">
-        <f t="shared" ref="AK60:AK65" si="52">SUM(AH60:AJ60)</f>
+        <f t="shared" ref="AK60" si="52">SUM(AH60:AJ60)</f>
         <v>252143</v>
       </c>
       <c r="AL60" s="5">
@@ -20110,43 +20098,140 @@
       <c r="C66" s="13">
         <v>46087</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
-      <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
+      <c r="D66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C66,0,"","auto")</f>
+        <v>200.49000549316406</v>
+      </c>
+      <c r="E66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C66,0,"","auto")</f>
+        <v>391.58999633789063</v>
+      </c>
+      <c r="F66" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C66,0,"","auto")</f>
+        <v>433056</v>
+      </c>
+      <c r="G66" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C66,0,"","auto")</f>
+        <v>221623</v>
+      </c>
+      <c r="H66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C66,0,"","auto")</f>
+        <v>44.509998321533203</v>
+      </c>
+      <c r="I66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C66,0,"","auto")</f>
+        <v>51.229999542236328</v>
+      </c>
+      <c r="J66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C66,0,"","auto")</f>
+        <v>61016</v>
+      </c>
+      <c r="K66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C66,0,"","auto")</f>
+        <v>137167</v>
+      </c>
+      <c r="L66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C66,0,"","auto")</f>
+        <v>1283.5</v>
+      </c>
+      <c r="M66" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C66,0,"","auto")</f>
+        <v>2230.389892578125</v>
+      </c>
+      <c r="N66" s="8">
+        <f t="shared" ref="N66" si="53">(J66+F66-F65)/(D66*H66/100)/1000</f>
+        <v>0.63295835764517094</v>
+      </c>
+      <c r="O66" s="8">
+        <f t="shared" ref="O66" si="54">(K66+G66-G65)/(E66*I66/100)/1000</f>
+        <v>0.63295457261264465</v>
+      </c>
+      <c r="P66" s="8">
+        <f t="shared" ref="P66" si="55">((J66+K66)+F66+G66-F65-G65)/(D66*H66/100+E66*I66/100)/1000</f>
+        <v>0.63295573793784743</v>
+      </c>
+      <c r="Q66" s="8">
+        <f t="shared" ref="Q66" si="56">P66*H66*10</f>
+        <v>281.72858833218402</v>
+      </c>
+      <c r="R66" s="8">
+        <f t="shared" ref="R66" si="57">P66*I66*10</f>
+        <v>324.26322164811779</v>
+      </c>
+      <c r="S66" s="4">
+        <f t="shared" ref="S66" si="58">((J66+K66)+F66+G66-F65-G65)/(D66+E66)</f>
+        <v>309.86015307497149</v>
+      </c>
+      <c r="T66" s="5">
+        <f t="shared" ref="T66" si="59">IF(AL66&lt;3000,0,AL66)</f>
+        <v>71739</v>
+      </c>
+      <c r="U66" s="5">
+        <f t="shared" ref="U66" si="60">IF(AM66&lt;3000,0,AM66)</f>
+        <v>85811</v>
+      </c>
+      <c r="V66" s="5">
+        <f t="shared" ref="V66" si="61">IF(AN66&lt;3000,0,AN66)</f>
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X66" s="7">
+        <f t="shared" ref="X66" si="62">J66+K66</f>
+        <v>198183</v>
+      </c>
+      <c r="Y66" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z66" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA66" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB66" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC66" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD66" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE66" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF66" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG66" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH66" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI66" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL66" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C66,0,"","auto")</f>
+        <v>71739</v>
+      </c>
+      <c r="AM66" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C66,0,"","auto")</f>
+        <v>85811</v>
+      </c>
+      <c r="AN66" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C66,0,"","auto")</f>
+        <v>41</v>
+      </c>
     </row>
     <row r="67" spans="2:40">
       <c r="B67" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -20240,43 +20240,140 @@
       <c r="C67" s="13">
         <v>46088</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="4"/>
-      <c r="AJ67" s="4"/>
-      <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
-      <c r="AM67" s="4"/>
-      <c r="AN67" s="4"/>
+      <c r="D67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C67,0,"","auto")</f>
+        <v>201.24795532226563</v>
+      </c>
+      <c r="E67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C67,0,"","auto")</f>
+        <v>562.180908203125</v>
+      </c>
+      <c r="F67" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C67,0,"","auto")</f>
+        <v>437307.8125</v>
+      </c>
+      <c r="G67" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C67,0,"","auto")</f>
+        <v>235281.59375</v>
+      </c>
+      <c r="H67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C67,0,"","auto")</f>
+        <v>44.749916076660156</v>
+      </c>
+      <c r="I67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C67,0,"","auto")</f>
+        <v>51.459812164306641</v>
+      </c>
+      <c r="J67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C67,0,"","auto")</f>
+        <v>50987.0859375</v>
+      </c>
+      <c r="K67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C67,0,"","auto")</f>
+        <v>163786.234375</v>
+      </c>
+      <c r="L67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C67,0,"","auto")</f>
+        <v>1513.0635986328125</v>
+      </c>
+      <c r="M67" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C67,0,"","auto")</f>
+        <v>2154.214111328125</v>
+      </c>
+      <c r="N67" s="8">
+        <f t="shared" ref="N67:N69" si="63">(J67+F67-F66)/(D67*H67/100)/1000</f>
+        <v>0.61336827242666914</v>
+      </c>
+      <c r="O67" s="8">
+        <f t="shared" ref="O67:O69" si="64">(K67+G67-G66)/(E67*I67/100)/1000</f>
+        <v>0.61336509294823482</v>
+      </c>
+      <c r="P67" s="8">
+        <f t="shared" ref="P67:P69" si="65">((J67+K67)+F67+G67-F66-G66)/(D67*H67/100+E67*I67/100)/1000</f>
+        <v>0.61336584775044911</v>
+      </c>
+      <c r="Q67" s="8">
+        <f t="shared" ref="Q67:Q69" si="66">P67*H67*10</f>
+        <v>274.48070211122109</v>
+      </c>
+      <c r="R67" s="8">
+        <f t="shared" ref="R67:R69" si="67">P67*I67*10</f>
+        <v>315.63691313238814</v>
+      </c>
+      <c r="S67" s="4">
+        <f t="shared" ref="S67:S69" si="68">((J67+K67)+F67+G67-F66-G66)/(D67+E67)</f>
+        <v>304.78769886693084</v>
+      </c>
+      <c r="T67" s="5">
+        <f t="shared" ref="T67:T69" si="69">IF(AL67&lt;3000,0,AL67)</f>
+        <v>0</v>
+      </c>
+      <c r="U67" s="5">
+        <f t="shared" ref="U67:U69" si="70">IF(AM67&lt;3000,0,AM67)</f>
+        <v>214874.09375</v>
+      </c>
+      <c r="V67" s="5">
+        <f t="shared" ref="V67:V69" si="71">IF(AN67&lt;3000,0,AN67)</f>
+        <v>0</v>
+      </c>
+      <c r="W67" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X67" s="7">
+        <f t="shared" ref="X67:X69" si="72">J67+K67</f>
+        <v>214773.3203125</v>
+      </c>
+      <c r="Y67" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z67" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA67" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB67" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC67" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD67" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE67" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF67" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG67" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH67" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI67" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL67" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C67,0,"","auto")</f>
+        <v>-106.99946594238281</v>
+      </c>
+      <c r="AM67" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C67,0,"","auto")</f>
+        <v>214874.09375</v>
+      </c>
+      <c r="AN67" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C67,0,"","auto")</f>
+        <v>6.0416664928197861E-3</v>
+      </c>
     </row>
     <row r="68" spans="2:40">
       <c r="B68" s="20">
@@ -20285,43 +20382,140 @@
       <c r="C68" s="13">
         <v>46089</v>
       </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AD68" s="4"/>
-      <c r="AE68" s="4"/>
-      <c r="AF68" s="4"/>
-      <c r="AG68" s="4"/>
-      <c r="AH68" s="4"/>
-      <c r="AI68" s="4"/>
-      <c r="AJ68" s="4"/>
-      <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
-      <c r="AM68" s="4"/>
-      <c r="AN68" s="4"/>
+      <c r="D68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C68,0,"","auto")</f>
+        <v>212.67330932617188</v>
+      </c>
+      <c r="E68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C68,0,"","auto")</f>
+        <v>563.45489501953125</v>
+      </c>
+      <c r="F68" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C68,0,"","auto")</f>
+        <v>444232.125</v>
+      </c>
+      <c r="G68" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C68,0,"","auto")</f>
+        <v>256321.984375</v>
+      </c>
+      <c r="H68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C68,0,"","auto")</f>
+        <v>44.630237579345703</v>
+      </c>
+      <c r="I68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C68,0,"","auto")</f>
+        <v>51.190254211425781</v>
+      </c>
+      <c r="J68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C68,0,"","auto")</f>
+        <v>55419.609375</v>
+      </c>
+      <c r="K68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C68,0,"","auto")</f>
+        <v>168410.265625</v>
+      </c>
+      <c r="L68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C68,0,"","auto")</f>
+        <v>1172.776123046875</v>
+      </c>
+      <c r="M68" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C68,0,"","auto")</f>
+        <v>2620.521728515625</v>
+      </c>
+      <c r="N68" s="8">
+        <f t="shared" si="63"/>
+        <v>0.6568284131535358</v>
+      </c>
+      <c r="O68" s="8">
+        <f t="shared" si="64"/>
+        <v>0.6568249955421811</v>
+      </c>
+      <c r="P68" s="8">
+        <f t="shared" si="65"/>
+        <v>0.65682584173379788</v>
+      </c>
+      <c r="Q68" s="8">
+        <f t="shared" si="66"/>
+        <v>293.14293364833122</v>
+      </c>
+      <c r="R68" s="8">
+        <f t="shared" si="67"/>
+        <v>336.23081810986832</v>
+      </c>
+      <c r="S68" s="4">
+        <f t="shared" si="68"/>
+        <v>324.4239504699737</v>
+      </c>
+      <c r="T68" s="5">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
+        <f t="shared" si="70"/>
+        <v>223406.296875</v>
+      </c>
+      <c r="V68" s="5">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="W68" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X68" s="7">
+        <f t="shared" si="72"/>
+        <v>223829.875</v>
+      </c>
+      <c r="Y68" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z68" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA68" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB68" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC68" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD68" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE68" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF68" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG68" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH68" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI68" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL68" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C68,0,"","auto")</f>
+        <v>-59.948276519775391</v>
+      </c>
+      <c r="AM68" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C68,0,"","auto")</f>
+        <v>223406.296875</v>
+      </c>
+      <c r="AN68" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C68,0,"","auto")</f>
+        <v>521.9931640625</v>
+      </c>
     </row>
     <row r="69" spans="2:40">
       <c r="B69" s="20">
@@ -20330,43 +20524,140 @@
       <c r="C69" s="13">
         <v>46090</v>
       </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
-      <c r="AF69" s="4"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="4"/>
-      <c r="AI69" s="4"/>
-      <c r="AJ69" s="4"/>
-      <c r="AK69" s="4"/>
-      <c r="AL69" s="4"/>
-      <c r="AM69" s="4"/>
-      <c r="AN69" s="4"/>
+      <c r="D69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C69,0,"","auto")</f>
+        <v>203.05000305175781</v>
+      </c>
+      <c r="E69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C69,0,"","auto")</f>
+        <v>556.09002685546875</v>
+      </c>
+      <c r="F69" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C69,0,"","auto")</f>
+        <v>460263</v>
+      </c>
+      <c r="G69" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C69,0,"","auto")</f>
+        <v>306661</v>
+      </c>
+      <c r="H69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C69,0,"","auto")</f>
+        <v>44.970001220703125</v>
+      </c>
+      <c r="I69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C69,0,"","auto")</f>
+        <v>51.560001373291016</v>
+      </c>
+      <c r="J69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C69,0,"","auto")</f>
+        <v>40466</v>
+      </c>
+      <c r="K69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C69,0,"","auto")</f>
+        <v>127066</v>
+      </c>
+      <c r="L69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C69,0,"","auto")</f>
+        <v>1138.300048828125</v>
+      </c>
+      <c r="M69" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C69,0,"","auto")</f>
+        <v>2076.449951171875</v>
+      </c>
+      <c r="N69" s="8">
+        <f t="shared" si="63"/>
+        <v>0.61872622862999382</v>
+      </c>
+      <c r="O69" s="8">
+        <f t="shared" si="64"/>
+        <v>0.61873953633302248</v>
+      </c>
+      <c r="P69" s="8">
+        <f t="shared" si="65"/>
+        <v>0.61873632192591621</v>
+      </c>
+      <c r="Q69" s="8">
+        <f t="shared" si="66"/>
+        <v>278.24573152301815</v>
+      </c>
+      <c r="R69" s="8">
+        <f t="shared" si="67"/>
+        <v>319.0204560820527</v>
+      </c>
+      <c r="S69" s="4">
+        <f t="shared" si="68"/>
+        <v>308.11428907731926</v>
+      </c>
+      <c r="T69" s="5">
+        <f t="shared" si="69"/>
+        <v>90808</v>
+      </c>
+      <c r="U69" s="5">
+        <f t="shared" si="70"/>
+        <v>76791</v>
+      </c>
+      <c r="V69" s="5">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="W69" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X69" s="7">
+        <f t="shared" si="72"/>
+        <v>167532</v>
+      </c>
+      <c r="Y69" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z69" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA69" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB69" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC69" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD69" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE69" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF69" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG69" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH69" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL69" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C69,0,"","auto")</f>
+        <v>90808</v>
+      </c>
+      <c r="AM69" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C69,0,"","auto")</f>
+        <v>76791</v>
+      </c>
+      <c r="AN69" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C69,0,"","auto")</f>
+        <v>-67</v>
+      </c>
     </row>
     <row r="70" spans="2:40">
       <c r="B70" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -20242,19 +20242,19 @@
       </c>
       <c r="D67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C67,0,"","auto")</f>
-        <v>201.24795532226563</v>
+        <v>201.21138000488281</v>
       </c>
       <c r="E67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C67,0,"","auto")</f>
-        <v>562.180908203125</v>
+        <v>562.21746826171875</v>
       </c>
       <c r="F67" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C67,0,"","auto")</f>
-        <v>437307.8125</v>
+        <v>437306.59375</v>
       </c>
       <c r="G67" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C67,0,"","auto")</f>
-        <v>235281.59375</v>
+        <v>235282.8125</v>
       </c>
       <c r="H67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C67,0,"","auto")</f>
@@ -20266,11 +20266,11 @@
       </c>
       <c r="J67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C67,0,"","auto")</f>
-        <v>50987.0859375</v>
+        <v>50977.296875</v>
       </c>
       <c r="K67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C67,0,"","auto")</f>
-        <v>163786.234375</v>
+        <v>163796.03125</v>
       </c>
       <c r="L67" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C67,0,"","auto")</f>
@@ -20281,47 +20281,47 @@
         <v>2154.214111328125</v>
       </c>
       <c r="N67" s="8">
-        <f t="shared" ref="N67:N69" si="63">(J67+F67-F66)/(D67*H67/100)/1000</f>
-        <v>0.61336827242666914</v>
+        <f t="shared" ref="N67:N70" si="63">(J67+F67-F66)/(D67*H67/100)/1000</f>
+        <v>0.6133575157260186</v>
       </c>
       <c r="O67" s="8">
-        <f t="shared" ref="O67:O69" si="64">(K67+G67-G66)/(E67*I67/100)/1000</f>
-        <v>0.61336509294823482</v>
+        <f t="shared" ref="O67:O70" si="64">(K67+G67-G66)/(E67*I67/100)/1000</f>
+        <v>0.61336328155604913</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" ref="P67:P69" si="65">((J67+K67)+F67+G67-F66-G66)/(D67*H67/100+E67*I67/100)/1000</f>
-        <v>0.61336584775044911</v>
+        <f t="shared" ref="P67:P70" si="65">((J67+K67)+F67+G67-F66-G66)/(D67*H67/100+E67*I67/100)/1000</f>
+        <v>0.61336191301641296</v>
       </c>
       <c r="Q67" s="8">
-        <f t="shared" ref="Q67:Q69" si="66">P67*H67*10</f>
-        <v>274.48070211122109</v>
+        <f t="shared" ref="Q67:Q70" si="66">P67*H67*10</f>
+        <v>274.47894132104204</v>
       </c>
       <c r="R67" s="8">
-        <f t="shared" ref="R67:R69" si="67">P67*I67*10</f>
-        <v>315.63691313238814</v>
+        <f t="shared" ref="R67:R70" si="67">P67*I67*10</f>
+        <v>315.634888325644</v>
       </c>
       <c r="S67" s="4">
-        <f t="shared" ref="S67:S69" si="68">((J67+K67)+F67+G67-F66-G66)/(D67+E67)</f>
-        <v>304.78769886693084</v>
+        <f t="shared" ref="S67:S70" si="68">((J67+K67)+F67+G67-F66-G66)/(D67+E67)</f>
+        <v>304.78771519221283</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" ref="T67:T69" si="69">IF(AL67&lt;3000,0,AL67)</f>
+        <f t="shared" ref="T67:T70" si="69">IF(AL67&lt;3000,0,AL67)</f>
         <v>0</v>
       </c>
       <c r="U67" s="5">
-        <f t="shared" ref="U67:U69" si="70">IF(AM67&lt;3000,0,AM67)</f>
+        <f t="shared" ref="U67:U70" si="70">IF(AM67&lt;3000,0,AM67)</f>
         <v>214874.09375</v>
       </c>
       <c r="V67" s="5">
-        <f t="shared" ref="V67:V69" si="71">IF(AN67&lt;3000,0,AN67)</f>
+        <f t="shared" ref="V67:V70" si="71">IF(AN67&lt;3000,0,AN67)</f>
         <v>0</v>
       </c>
       <c r="W67" s="5" t="s">
         <v>53</v>
       </c>
       <c r="X67" s="7">
-        <f t="shared" ref="X67:X69" si="72">J67+K67</f>
-        <v>214773.3203125</v>
+        <f t="shared" ref="X67:X70" si="72">J67+K67</f>
+        <v>214773.328125</v>
       </c>
       <c r="Y67" s="4">
         <v>0.61699999999999999</v>
@@ -20384,19 +20384,19 @@
       </c>
       <c r="D68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C68,0,"","auto")</f>
-        <v>212.67330932617188</v>
+        <v>160.03988647460938</v>
       </c>
       <c r="E68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C68,0,"","auto")</f>
-        <v>563.45489501953125</v>
+        <v>616.08831787109375</v>
       </c>
       <c r="F68" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C68,0,"","auto")</f>
-        <v>444232.125</v>
+        <v>442472.15625</v>
       </c>
       <c r="G68" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C68,0,"","auto")</f>
-        <v>256321.984375</v>
+        <v>258081.984375</v>
       </c>
       <c r="H68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C68,0,"","auto")</f>
@@ -20408,11 +20408,11 @@
       </c>
       <c r="J68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C68,0,"","auto")</f>
-        <v>55419.609375</v>
+        <v>41330.3984375</v>
       </c>
       <c r="K68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C68,0,"","auto")</f>
-        <v>168410.265625</v>
+        <v>182499.484375</v>
       </c>
       <c r="L68" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C68,0,"","auto")</f>
@@ -20424,27 +20424,27 @@
       </c>
       <c r="N68" s="8">
         <f t="shared" si="63"/>
-        <v>0.6568284131535358</v>
+        <v>0.65096523326645894</v>
       </c>
       <c r="O68" s="8">
         <f t="shared" si="64"/>
-        <v>0.6568249955421811</v>
+        <v>0.65096231375537694</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="65"/>
-        <v>0.65682584173379788</v>
+        <v>0.65096285286530053</v>
       </c>
       <c r="Q68" s="8">
         <f t="shared" si="66"/>
-        <v>293.14293364833122</v>
+        <v>290.5262677870702</v>
       </c>
       <c r="R68" s="8">
         <f t="shared" si="67"/>
-        <v>336.23081810986832</v>
+        <v>333.2295392036969</v>
       </c>
       <c r="S68" s="4">
         <f t="shared" si="68"/>
-        <v>324.4239504699737</v>
+        <v>324.42400079993178</v>
       </c>
       <c r="T68" s="5">
         <f t="shared" si="69"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="X68" s="7">
         <f t="shared" si="72"/>
-        <v>223829.875</v>
+        <v>223829.8828125</v>
       </c>
       <c r="Y68" s="4">
         <v>0.61699999999999999</v>
@@ -20526,67 +20526,67 @@
       </c>
       <c r="D69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C69,0,"","auto")</f>
-        <v>203.05000305175781</v>
+        <v>203.01661682128906</v>
       </c>
       <c r="E69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C69,0,"","auto")</f>
-        <v>556.09002685546875</v>
+        <v>555.98388671875</v>
       </c>
       <c r="F69" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C69,0,"","auto")</f>
-        <v>460263</v>
+        <v>458506.3125</v>
       </c>
       <c r="G69" s="7">
         <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C69,0,"","auto")</f>
-        <v>306661</v>
+        <v>308427.0625</v>
       </c>
       <c r="H69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C69,0,"","auto")</f>
-        <v>44.970001220703125</v>
+        <v>44.969474792480469</v>
       </c>
       <c r="I69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C69,0,"","auto")</f>
-        <v>51.560001373291016</v>
+        <v>51.560153961181641</v>
       </c>
       <c r="J69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C69,0,"","auto")</f>
-        <v>40466</v>
+        <v>40465.6015625</v>
       </c>
       <c r="K69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C69,0,"","auto")</f>
-        <v>127066</v>
+        <v>127062.1953125</v>
       </c>
       <c r="L69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C69,0,"","auto")</f>
-        <v>1138.300048828125</v>
+        <v>1138.440673828125</v>
       </c>
       <c r="M69" s="6">
         <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C69,0,"","auto")</f>
-        <v>2076.449951171875</v>
+        <v>2076.8642578125</v>
       </c>
       <c r="N69" s="8">
         <f t="shared" si="63"/>
-        <v>0.61872622862999382</v>
+        <v>0.61886679954160884</v>
       </c>
       <c r="O69" s="8">
         <f t="shared" si="64"/>
-        <v>0.61873953633302248</v>
+        <v>0.61886370148849901</v>
       </c>
       <c r="P69" s="8">
         <f t="shared" si="65"/>
-        <v>0.61873632192591621</v>
+        <v>0.61886444981395494</v>
       </c>
       <c r="Q69" s="8">
         <f t="shared" si="66"/>
-        <v>278.24573152301815</v>
+        <v>278.30009275870941</v>
       </c>
       <c r="R69" s="8">
         <f t="shared" si="67"/>
-        <v>319.0204560820527</v>
+        <v>319.08746313509488</v>
       </c>
       <c r="S69" s="4">
         <f t="shared" si="68"/>
-        <v>308.11428907731926</v>
+        <v>308.17770233226315</v>
       </c>
       <c r="T69" s="5">
         <f t="shared" si="69"/>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="X69" s="7">
         <f t="shared" si="72"/>
-        <v>167532</v>
+        <v>167527.796875</v>
       </c>
       <c r="Y69" s="4">
         <v>0.61699999999999999</v>
@@ -20666,34 +20666,110 @@
       <c r="C70" s="13">
         <v>46091</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
-      <c r="Z70" s="4"/>
-      <c r="AA70" s="4"/>
-      <c r="AB70" s="4"/>
-      <c r="AC70" s="4"/>
-      <c r="AD70" s="4"/>
-      <c r="AE70" s="4"/>
+      <c r="D70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C70,0,"","auto")</f>
+        <v>154.97999572753906</v>
+      </c>
+      <c r="E70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C70,0,"","auto")</f>
+        <v>403.27999877929688</v>
+      </c>
+      <c r="F70" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C70,0,"","auto")</f>
+        <v>461840</v>
+      </c>
+      <c r="G70" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C70,0,"","auto")</f>
+        <v>318587</v>
+      </c>
+      <c r="H70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C70,0,"","auto")</f>
+        <v>44.209999084472656</v>
+      </c>
+      <c r="I70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C70,0,"","auto")</f>
+        <v>51.779998779296875</v>
+      </c>
+      <c r="J70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C70,0,"","auto")</f>
+        <v>39894</v>
+      </c>
+      <c r="K70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C70,0,"","auto")</f>
+        <v>121584</v>
+      </c>
+      <c r="L70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C70,0,"","auto")</f>
+        <v>1340.800048828125</v>
+      </c>
+      <c r="M70" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C70,0,"","auto")</f>
+        <v>2687.570068359375</v>
+      </c>
+      <c r="N70" s="8">
+        <f t="shared" si="63"/>
+        <v>0.63090773614320561</v>
+      </c>
+      <c r="O70" s="8">
+        <f t="shared" si="64"/>
+        <v>0.63090202347613999</v>
+      </c>
+      <c r="P70" s="8">
+        <f t="shared" si="65"/>
+        <v>0.63090343481185285</v>
+      </c>
+      <c r="Q70" s="8">
+        <f t="shared" si="66"/>
+        <v>278.92240275422671</v>
+      </c>
+      <c r="R70" s="8">
+        <f t="shared" si="67"/>
+        <v>326.68179084411946</v>
+      </c>
+      <c r="S70" s="4">
+        <f t="shared" si="68"/>
+        <v>313.42318403913043</v>
+      </c>
+      <c r="T70" s="5">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="U70" s="5">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="V70" s="5">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="W70" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X70" s="7">
+        <f t="shared" si="72"/>
+        <v>161478</v>
+      </c>
+      <c r="Y70" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z70" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA70" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB70" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC70" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD70" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE70" s="4">
+        <v>52.51</v>
+      </c>
       <c r="AF70" s="4"/>
       <c r="AG70" s="4"/>
       <c r="AH70" s="4"/>

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Desktop\ฝึกสร้างเว็บ\Daily_DC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Desktop\Python_Project\Daily_DC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1249,6 +1249,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1339,7 +1340,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000025-06C4-4EBD-9DB5-5F6028942F55}"/>
                 </c:ext>
@@ -1361,7 +1364,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1662,6 +1667,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1670,7 +1676,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1678,6 +1686,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1686,7 +1695,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -2104,6 +2115,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2210,6 +2222,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2274,6 +2287,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2282,7 +2296,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000018-B8D4-4943-8087-5038E5DF57F4}"/>
                 </c:ext>
@@ -2290,6 +2306,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2298,7 +2315,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{0000000A-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2599,6 +2618,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:numFmt formatCode="#,##0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -2634,7 +2654,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{0000000B-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2933,6 +2955,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2941,7 +2964,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2963,7 +2988,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -3265,6 +3292,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:numFmt formatCode="#,##0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3300,7 +3328,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -3719,6 +3749,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5438,6 +5469,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5502,6 +5534,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5510,7 +5543,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000008-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5518,6 +5553,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5526,7 +5562,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5826,6 +5864,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5834,7 +5873,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -6252,6 +6293,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7294,6 +7336,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7358,6 +7401,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7366,7 +7410,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-E73E-4A56-8161-D7588DDD0A4F}"/>
                 </c:ext>
@@ -7374,6 +7420,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7382,7 +7429,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -7682,6 +7731,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7690,7 +7740,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -8108,6 +8160,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -20732,11 +20785,11 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>82860</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>78697</v>
       </c>
       <c r="V70" s="5">
         <f t="shared" si="71"/>
@@ -20770,15 +20823,36 @@
       <c r="AE70" s="4">
         <v>52.51</v>
       </c>
-      <c r="AF70" s="4"/>
-      <c r="AG70" s="4"/>
-      <c r="AH70" s="4"/>
-      <c r="AI70" s="4"/>
-      <c r="AJ70" s="4"/>
-      <c r="AK70" s="4"/>
-      <c r="AL70" s="4"/>
-      <c r="AM70" s="4"/>
-      <c r="AN70" s="4"/>
+      <c r="AF70" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG70" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH70" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL70" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C70,0,"","auto")</f>
+        <v>82860</v>
+      </c>
+      <c r="AM70" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C70,0,"","auto")</f>
+        <v>78697</v>
+      </c>
+      <c r="AN70" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C70,0,"","auto")</f>
+        <v>-79</v>
+      </c>
     </row>
     <row r="71" spans="2:40">
       <c r="B71" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -1249,7 +1249,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1340,9 +1339,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000025-06C4-4EBD-9DB5-5F6028942F55}"/>
                 </c:ext>
@@ -1364,9 +1361,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1667,7 +1662,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1676,9 +1670,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -1686,7 +1678,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -1695,9 +1686,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-3293-492F-8385-7317FCBDA947}"/>
                 </c:ext>
@@ -2115,7 +2104,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2222,7 +2210,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2287,7 +2274,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2296,9 +2282,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000018-B8D4-4943-8087-5038E5DF57F4}"/>
                 </c:ext>
@@ -2306,7 +2290,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2315,9 +2298,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{0000000A-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2618,7 +2599,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:numFmt formatCode="#,##0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -2654,9 +2634,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{0000000B-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2955,7 +2933,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -2964,9 +2941,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -2988,9 +2963,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -3292,7 +3265,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:numFmt formatCode="#,##0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3328,9 +3300,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-C1AA-4BA1-B9D7-0FA9D080A20B}"/>
                 </c:ext>
@@ -3749,7 +3719,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3856,7 +3825,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3921,7 +3889,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -3930,9 +3897,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000016-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -3940,7 +3905,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -3949,9 +3913,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000012-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4251,7 +4213,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4260,9 +4221,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000015-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4270,7 +4229,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4279,9 +4237,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000013-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4579,7 +4535,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4588,9 +4543,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4598,7 +4551,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4607,9 +4559,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4910,7 +4860,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4919,9 +4868,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000014-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -4929,7 +4876,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4938,9 +4884,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-48A3-4227-866C-E3F61A29B8C1}"/>
                 </c:ext>
@@ -5357,7 +5301,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5469,7 +5412,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5534,7 +5476,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5543,9 +5484,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000008-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5553,7 +5492,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5562,9 +5500,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -5864,7 +5800,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -5873,9 +5808,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-F8C4-45AB-8B58-07FEC847C1C3}"/>
                 </c:ext>
@@ -6293,7 +6226,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7336,7 +7268,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7401,7 +7332,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7410,9 +7340,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-E73E-4A56-8161-D7588DDD0A4F}"/>
                 </c:ext>
@@ -7420,7 +7348,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7429,9 +7356,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -7731,7 +7656,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7740,9 +7664,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -8160,7 +8082,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -20861,43 +20782,140 @@
       <c r="C71" s="13">
         <v>46092</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
-      <c r="X71" s="4"/>
-      <c r="Y71" s="4"/>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="4"/>
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="4"/>
-      <c r="AD71" s="4"/>
-      <c r="AE71" s="4"/>
-      <c r="AF71" s="4"/>
-      <c r="AG71" s="4"/>
-      <c r="AH71" s="4"/>
-      <c r="AI71" s="4"/>
-      <c r="AJ71" s="4"/>
-      <c r="AK71" s="4"/>
-      <c r="AL71" s="4"/>
-      <c r="AM71" s="4"/>
-      <c r="AN71" s="4"/>
+      <c r="D71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C71,0,"","auto")</f>
+        <v>210.03469848632813</v>
+      </c>
+      <c r="E71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C71,0,"","auto")</f>
+        <v>565.40948486328125</v>
+      </c>
+      <c r="F71" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C71,0,"","auto")</f>
+        <v>466073.34375</v>
+      </c>
+      <c r="G71" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C71,0,"","auto")</f>
+        <v>331707.34375</v>
+      </c>
+      <c r="H71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C71,0,"","auto")</f>
+        <v>44.519798278808594</v>
+      </c>
+      <c r="I71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C71,0,"","auto")</f>
+        <v>51.249958038330078</v>
+      </c>
+      <c r="J71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C71,0,"","auto")</f>
+        <v>54076.6015625</v>
+      </c>
+      <c r="K71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C71,0,"","auto")</f>
+        <v>167579.375</v>
+      </c>
+      <c r="L71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C71,0,"","auto")</f>
+        <v>1561.0513916015625</v>
+      </c>
+      <c r="M71" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C71,0,"","auto")</f>
+        <v>2418.006591796875</v>
+      </c>
+      <c r="N71" s="8">
+        <f t="shared" ref="N71:N73" si="73">(J71+F71-F70)/(D71*H71/100)/1000</f>
+        <v>0.62358893233094947</v>
+      </c>
+      <c r="O71" s="8">
+        <f t="shared" ref="O71:O73" si="74">(K71+G71-G70)/(E71*I71/100)/1000</f>
+        <v>0.62359248508631171</v>
+      </c>
+      <c r="P71" s="8">
+        <f t="shared" ref="P71:P73" si="75">((J71+K71)+F71+G71-F70-G70)/(D71*H71/100+E71*I71/100)/1000</f>
+        <v>0.62359161833532062</v>
+      </c>
+      <c r="Q71" s="8">
+        <f t="shared" ref="Q71:Q73" si="76">P71*H71*10</f>
+        <v>277.62173056644269</v>
+      </c>
+      <c r="R71" s="8">
+        <f t="shared" ref="R71:R73" si="77">P71*I71*10</f>
+        <v>319.59044272739527</v>
+      </c>
+      <c r="S71" s="4">
+        <f t="shared" ref="S71:S73" si="78">((J71+K71)+F71+G71-F70-G70)/(D71+E71)</f>
+        <v>308.22291171245058</v>
+      </c>
+      <c r="T71" s="5">
+        <f t="shared" ref="T71:T73" si="79">IF(AL71&lt;3000,0,AL71)</f>
+        <v>0</v>
+      </c>
+      <c r="U71" s="5">
+        <f t="shared" ref="U71:U73" si="80">IF(AM71&lt;3000,0,AM71)</f>
+        <v>222550.96875</v>
+      </c>
+      <c r="V71" s="5">
+        <f t="shared" ref="V71:V73" si="81">IF(AN71&lt;3000,0,AN71)</f>
+        <v>0</v>
+      </c>
+      <c r="W71" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X71" s="7">
+        <f t="shared" ref="X71:X73" si="82">J71+K71</f>
+        <v>221655.9765625</v>
+      </c>
+      <c r="Y71" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD71" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE71" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF71" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG71" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH71" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL71" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C71,0,"","auto")</f>
+        <v>-683.9881591796875</v>
+      </c>
+      <c r="AM71" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C71,0,"","auto")</f>
+        <v>222550.96875</v>
+      </c>
+      <c r="AN71" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C71,0,"","auto")</f>
+        <v>-209.99737548828125</v>
+      </c>
     </row>
     <row r="72" spans="2:40">
       <c r="B72" s="20">
@@ -20906,43 +20924,140 @@
       <c r="C72" s="13">
         <v>46093</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
-      <c r="Y72" s="4"/>
-      <c r="Z72" s="4"/>
-      <c r="AA72" s="4"/>
-      <c r="AB72" s="4"/>
-      <c r="AC72" s="4"/>
-      <c r="AD72" s="4"/>
-      <c r="AE72" s="4"/>
-      <c r="AF72" s="4"/>
-      <c r="AG72" s="4"/>
-      <c r="AH72" s="4"/>
-      <c r="AI72" s="4"/>
-      <c r="AJ72" s="4"/>
-      <c r="AK72" s="4"/>
-      <c r="AL72" s="4"/>
-      <c r="AM72" s="4"/>
-      <c r="AN72" s="4"/>
+      <c r="D72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C72,0,"","auto")</f>
+        <v>202.41732788085938</v>
+      </c>
+      <c r="E72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C72,0,"","auto")</f>
+        <v>564.73193359375</v>
+      </c>
+      <c r="F72" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C72,0,"","auto")</f>
+        <v>468013.46875</v>
+      </c>
+      <c r="G72" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C72,0,"","auto")</f>
+        <v>337969.90625</v>
+      </c>
+      <c r="H72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C72,0,"","auto")</f>
+        <v>44.230270385742188</v>
+      </c>
+      <c r="I72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C72,0,"","auto")</f>
+        <v>51.190135955810547</v>
+      </c>
+      <c r="J72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C72,0,"","auto")</f>
+        <v>52060.75390625</v>
+      </c>
+      <c r="K72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C72,0,"","auto")</f>
+        <v>168101.390625</v>
+      </c>
+      <c r="L72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C72,0,"","auto")</f>
+        <v>1634.8289794921875</v>
+      </c>
+      <c r="M72" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C72,0,"","auto")</f>
+        <v>2111.0537109375</v>
+      </c>
+      <c r="N72" s="8">
+        <f t="shared" si="73"/>
+        <v>0.60316140844111066</v>
+      </c>
+      <c r="O72" s="8">
+        <f t="shared" si="74"/>
+        <v>0.60315381261991219</v>
+      </c>
+      <c r="P72" s="8">
+        <f t="shared" si="75"/>
+        <v>0.60315560876808871</v>
+      </c>
+      <c r="Q72" s="8">
+        <f t="shared" si="76"/>
+        <v>266.77735660489498</v>
+      </c>
+      <c r="R72" s="8">
+        <f t="shared" si="77"/>
+        <v>308.75617615348136</v>
+      </c>
+      <c r="S72" s="4">
+        <f t="shared" si="78"/>
+        <v>297.6797912733287</v>
+      </c>
+      <c r="T72" s="5">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="U72" s="5">
+        <f t="shared" si="80"/>
+        <v>219818</v>
+      </c>
+      <c r="V72" s="5">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X72" s="7">
+        <f t="shared" si="82"/>
+        <v>220162.14453125</v>
+      </c>
+      <c r="Y72" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z72" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA72" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB72" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC72" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD72" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE72" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF72" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG72" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH72" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI72" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL72" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C72,0,"","auto")</f>
+        <v>338</v>
+      </c>
+      <c r="AM72" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C72,0,"","auto")</f>
+        <v>219818</v>
+      </c>
+      <c r="AN72" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C72,0,"","auto")</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="73" spans="2:40">
       <c r="B73" s="20">
@@ -20951,43 +21066,140 @@
       <c r="C73" s="13">
         <v>46094</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
-      <c r="Z73" s="4"/>
-      <c r="AA73" s="4"/>
-      <c r="AB73" s="4"/>
-      <c r="AC73" s="4"/>
-      <c r="AD73" s="4"/>
-      <c r="AE73" s="4"/>
-      <c r="AF73" s="4"/>
-      <c r="AG73" s="4"/>
-      <c r="AH73" s="4"/>
-      <c r="AI73" s="4"/>
-      <c r="AJ73" s="4"/>
-      <c r="AK73" s="4"/>
-      <c r="AL73" s="4"/>
-      <c r="AM73" s="4"/>
-      <c r="AN73" s="4"/>
+      <c r="D73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C73,0,"","auto")</f>
+        <v>212.94999694824219</v>
+      </c>
+      <c r="E73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C73,0,"","auto")</f>
+        <v>567.52001953125</v>
+      </c>
+      <c r="F73" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C73,0,"","auto")</f>
+        <v>478750</v>
+      </c>
+      <c r="G73" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C73,0,"","auto")</f>
+        <v>370924</v>
+      </c>
+      <c r="H73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C73,0,"","auto")</f>
+        <v>44.619998931884766</v>
+      </c>
+      <c r="I73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C73,0,"","auto")</f>
+        <v>51.389999389648438</v>
+      </c>
+      <c r="J73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C73,0,"","auto")</f>
+        <v>50265</v>
+      </c>
+      <c r="K73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C73,0,"","auto")</f>
+        <v>154284</v>
+      </c>
+      <c r="L73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C73,0,"","auto")</f>
+        <v>1489.4599609375</v>
+      </c>
+      <c r="M73" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C73,0,"","auto")</f>
+        <v>2260.419921875</v>
+      </c>
+      <c r="N73" s="8">
+        <f t="shared" si="73"/>
+        <v>0.641997804680149</v>
+      </c>
+      <c r="O73" s="8">
+        <f t="shared" si="74"/>
+        <v>0.64199908984277332</v>
+      </c>
+      <c r="P73" s="8">
+        <f t="shared" si="75"/>
+        <v>0.64199877403095895</v>
+      </c>
+      <c r="Q73" s="8">
+        <f t="shared" si="76"/>
+        <v>286.4598461153272</v>
+      </c>
+      <c r="R73" s="8">
+        <f t="shared" si="77"/>
+        <v>329.92316605606027</v>
+      </c>
+      <c r="S73" s="4">
+        <f t="shared" si="78"/>
+        <v>318.06426865665867</v>
+      </c>
+      <c r="T73" s="5">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="5">
+        <f t="shared" si="80"/>
+        <v>219818</v>
+      </c>
+      <c r="V73" s="5">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="W73" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X73" s="7">
+        <f t="shared" si="82"/>
+        <v>204549</v>
+      </c>
+      <c r="Y73" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z73" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA73" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB73" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC73" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD73" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE73" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF73" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG73" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH73" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI73" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL73" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C73,0,"","auto")</f>
+        <v>338</v>
+      </c>
+      <c r="AM73" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C73,0,"","auto")</f>
+        <v>219818</v>
+      </c>
+      <c r="AN73" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C73,0,"","auto")</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="74" spans="2:40">
       <c r="B74" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -6337,7 +6337,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6402,7 +6401,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6411,9 +6409,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-DDA2-42C6-9491-EA0926A527DF}"/>
                 </c:ext>
@@ -6421,7 +6417,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6430,9 +6425,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-8A28-4297-AE44-C665D87E7819}"/>
                 </c:ext>
@@ -6732,7 +6725,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
-              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6741,9 +6733,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-8A28-4297-AE44-C665D87E7819}"/>
                 </c:ext>
@@ -7161,7 +7151,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -21208,43 +21197,140 @@
       <c r="C74" s="13">
         <v>46095</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
-      <c r="Z74" s="4"/>
-      <c r="AA74" s="4"/>
-      <c r="AB74" s="4"/>
-      <c r="AC74" s="4"/>
-      <c r="AD74" s="4"/>
-      <c r="AE74" s="4"/>
-      <c r="AF74" s="4"/>
-      <c r="AG74" s="4"/>
-      <c r="AH74" s="4"/>
-      <c r="AI74" s="4"/>
-      <c r="AJ74" s="4"/>
-      <c r="AK74" s="4"/>
-      <c r="AL74" s="4"/>
-      <c r="AM74" s="4"/>
-      <c r="AN74" s="4"/>
+      <c r="D74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C74,0,"","auto")</f>
+        <v>202.03756713867188</v>
+      </c>
+      <c r="E74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C74,0,"","auto")</f>
+        <v>564.66912841796875</v>
+      </c>
+      <c r="F74" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C74,0,"","auto")</f>
+        <v>487536.9375</v>
+      </c>
+      <c r="G74" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C74,0,"","auto")</f>
+        <v>399484.96875</v>
+      </c>
+      <c r="H74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C74,0,"","auto")</f>
+        <v>44.330093383789063</v>
+      </c>
+      <c r="I74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C74,0,"","auto")</f>
+        <v>51.549709320068359</v>
+      </c>
+      <c r="J74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C74,0,"","auto")</f>
+        <v>47768.91015625</v>
+      </c>
+      <c r="K74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C74,0,"","auto")</f>
+        <v>155249</v>
+      </c>
+      <c r="L74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C74,0,"","auto")</f>
+        <v>1327.40185546875</v>
+      </c>
+      <c r="M74" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C74,0,"","auto")</f>
+        <v>2479.1328125</v>
+      </c>
+      <c r="N74" s="8">
+        <f t="shared" ref="N74:N76" si="83">(J74+F74-F73)/(D74*H74/100)/1000</f>
+        <v>0.63146130025630531</v>
+      </c>
+      <c r="O74" s="8">
+        <f t="shared" ref="O74:O76" si="84">(K74+G74-G73)/(E74*I74/100)/1000</f>
+        <v>0.63146429014777827</v>
+      </c>
+      <c r="P74" s="8">
+        <f t="shared" ref="P74:P76" si="85">((J74+K74)+F74+G74-F73-G73)/(D74*H74/100+E74*I74/100)/1000</f>
+        <v>0.63146358665149305</v>
+      </c>
+      <c r="Q74" s="8">
+        <f t="shared" ref="Q74:Q76" si="86">P74*H74*10</f>
+        <v>279.92839764723061</v>
+      </c>
+      <c r="R74" s="8">
+        <f t="shared" ref="R74:R76" si="87">P74*I74*10</f>
+        <v>325.51764338092261</v>
+      </c>
+      <c r="S74" s="4">
+        <f t="shared" ref="S74:S76" si="88">((J74+K74)+F74+G74-F73-G73)/(D74+E74)</f>
+        <v>313.50426153738073</v>
+      </c>
+      <c r="T74" s="5">
+        <f t="shared" ref="T74:T76" si="89">IF(AL74&lt;3000,0,AL74)</f>
+        <v>22706</v>
+      </c>
+      <c r="U74" s="5">
+        <f t="shared" ref="U74:U76" si="90">IF(AM74&lt;3000,0,AM74)</f>
+        <v>179892</v>
+      </c>
+      <c r="V74" s="5">
+        <f t="shared" ref="V74:V76" si="91">IF(AN74&lt;3000,0,AN74)</f>
+        <v>0</v>
+      </c>
+      <c r="W74" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X74" s="7">
+        <f t="shared" ref="X74:X76" si="92">J74+K74</f>
+        <v>203017.91015625</v>
+      </c>
+      <c r="Y74" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z74" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA74" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB74" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC74" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD74" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE74" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF74" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG74" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH74" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL74" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C74,0,"","auto")</f>
+        <v>22706</v>
+      </c>
+      <c r="AM74" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C74,0,"","auto")</f>
+        <v>179892</v>
+      </c>
+      <c r="AN74" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C74,0,"","auto")</f>
+        <v>415</v>
+      </c>
     </row>
     <row r="75" spans="2:40">
       <c r="B75" s="20">
@@ -21253,43 +21339,140 @@
       <c r="C75" s="13">
         <v>46096</v>
       </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="4"/>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
-      <c r="AD75" s="4"/>
-      <c r="AE75" s="4"/>
-      <c r="AF75" s="4"/>
-      <c r="AG75" s="4"/>
-      <c r="AH75" s="4"/>
-      <c r="AI75" s="4"/>
-      <c r="AJ75" s="4"/>
-      <c r="AK75" s="4"/>
-      <c r="AL75" s="4"/>
-      <c r="AM75" s="4"/>
-      <c r="AN75" s="4"/>
+      <c r="D75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C75,0,"","auto")</f>
+        <v>212.88650512695313</v>
+      </c>
+      <c r="E75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C75,0,"","auto")</f>
+        <v>563.368408203125</v>
+      </c>
+      <c r="F75" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C75,0,"","auto")</f>
+        <v>494620.21875</v>
+      </c>
+      <c r="G75" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C75,0,"","auto")</f>
+        <v>421039.625</v>
+      </c>
+      <c r="H75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C75,0,"","auto")</f>
+        <v>44.460277557373047</v>
+      </c>
+      <c r="I75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C75,0,"","auto")</f>
+        <v>51.130256652832031</v>
+      </c>
+      <c r="J75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C75,0,"","auto")</f>
+        <v>51949.5546875</v>
+      </c>
+      <c r="K75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C75,0,"","auto")</f>
+        <v>158098.328125</v>
+      </c>
+      <c r="L75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C75,0,"","auto")</f>
+        <v>1617.776123046875</v>
+      </c>
+      <c r="M75" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C75,0,"","auto")</f>
+        <v>2540.553955078125</v>
+      </c>
+      <c r="N75" s="8">
+        <f t="shared" si="83"/>
+        <v>0.62369655503561583</v>
+      </c>
+      <c r="O75" s="8">
+        <f t="shared" si="84"/>
+        <v>0.62368309667195043</v>
+      </c>
+      <c r="P75" s="8">
+        <f t="shared" si="85"/>
+        <v>0.62368642520009465</v>
+      </c>
+      <c r="Q75" s="8">
+        <f t="shared" si="86"/>
+        <v>277.29271573161992</v>
+      </c>
+      <c r="R75" s="8">
+        <f t="shared" si="87"/>
+        <v>318.89246991368168</v>
+      </c>
+      <c r="S75" s="4">
+        <f t="shared" si="88"/>
+        <v>307.48381261582603</v>
+      </c>
+      <c r="T75" s="5">
+        <f t="shared" si="89"/>
+        <v>22706</v>
+      </c>
+      <c r="U75" s="5">
+        <f t="shared" si="90"/>
+        <v>179892</v>
+      </c>
+      <c r="V75" s="5">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W75" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X75" s="7">
+        <f t="shared" si="92"/>
+        <v>210047.8828125</v>
+      </c>
+      <c r="Y75" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD75" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE75" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF75" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG75" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH75" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL75" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C75,0,"","auto")</f>
+        <v>22706</v>
+      </c>
+      <c r="AM75" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C75,0,"","auto")</f>
+        <v>179892</v>
+      </c>
+      <c r="AN75" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C75,0,"","auto")</f>
+        <v>415</v>
+      </c>
     </row>
     <row r="76" spans="2:40">
       <c r="B76" s="20">
@@ -21298,43 +21481,140 @@
       <c r="C76" s="13">
         <v>46097</v>
       </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
-      <c r="AD76" s="4"/>
-      <c r="AE76" s="4"/>
-      <c r="AF76" s="4"/>
-      <c r="AG76" s="4"/>
-      <c r="AH76" s="4"/>
-      <c r="AI76" s="4"/>
-      <c r="AJ76" s="4"/>
-      <c r="AK76" s="4"/>
-      <c r="AL76" s="4"/>
-      <c r="AM76" s="4"/>
-      <c r="AN76" s="4"/>
+      <c r="D76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C76,0,"","auto")</f>
+        <v>164.69999694824219</v>
+      </c>
+      <c r="E76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C76,0,"","auto")</f>
+        <v>431.55999755859375</v>
+      </c>
+      <c r="F76" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C76,0,"","auto")</f>
+        <v>492043</v>
+      </c>
+      <c r="G76" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C76,0,"","auto")</f>
+        <v>413289</v>
+      </c>
+      <c r="H76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C76,0,"","auto")</f>
+        <v>44.860000610351563</v>
+      </c>
+      <c r="I76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C76,0,"","auto")</f>
+        <v>51.5</v>
+      </c>
+      <c r="J76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C76,0,"","auto")</f>
+        <v>41236</v>
+      </c>
+      <c r="K76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C76,0,"","auto")</f>
+        <v>124044</v>
+      </c>
+      <c r="L76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C76,0,"","auto")</f>
+        <v>1295.699951171875</v>
+      </c>
+      <c r="M76" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C76,0,"","auto")</f>
+        <v>2373.60009765625</v>
+      </c>
+      <c r="N76" s="8">
+        <f t="shared" si="83"/>
+        <v>0.52323319910119492</v>
+      </c>
+      <c r="O76" s="8">
+        <f t="shared" si="84"/>
+        <v>0.52324677893742388</v>
+      </c>
+      <c r="P76" s="8">
+        <f t="shared" si="85"/>
+        <v>0.52324339085844085</v>
+      </c>
+      <c r="Q76" s="8">
+        <f t="shared" si="86"/>
+        <v>234.72698833272077</v>
+      </c>
+      <c r="R76" s="8">
+        <f t="shared" si="87"/>
+        <v>269.47034629209702</v>
+      </c>
+      <c r="S76" s="4">
+        <f t="shared" si="88"/>
+        <v>259.87347411788085</v>
+      </c>
+      <c r="T76" s="5">
+        <f t="shared" si="89"/>
+        <v>22706</v>
+      </c>
+      <c r="U76" s="5">
+        <f t="shared" si="90"/>
+        <v>179892</v>
+      </c>
+      <c r="V76" s="5">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W76" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X76" s="7">
+        <f t="shared" si="92"/>
+        <v>165280</v>
+      </c>
+      <c r="Y76" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD76" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE76" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF76" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG76" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH76" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL76" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C76,0,"","auto")</f>
+        <v>22706</v>
+      </c>
+      <c r="AM76" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C76,0,"","auto")</f>
+        <v>179892</v>
+      </c>
+      <c r="AN76" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C76,0,"","auto")</f>
+        <v>415</v>
+      </c>
     </row>
     <row r="77" spans="2:40">
       <c r="B77" s="20">

--- a/Actual vs Plan.xlsx
+++ b/Actual vs Plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -6337,6 +6337,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6401,6 +6402,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6409,7 +6411,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-DDA2-42C6-9491-EA0926A527DF}"/>
                 </c:ext>
@@ -6417,6 +6421,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6425,7 +6430,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000004-8A28-4297-AE44-C665D87E7819}"/>
                 </c:ext>
@@ -6725,6 +6732,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -6733,7 +6741,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-8A28-4297-AE44-C665D87E7819}"/>
                 </c:ext>
@@ -7151,6 +7161,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7257,6 +7268,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7321,6 +7333,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7329,7 +7342,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-E73E-4A56-8161-D7588DDD0A4F}"/>
                 </c:ext>
@@ -7337,6 +7352,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7345,7 +7361,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -7645,6 +7663,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="30"/>
+              <c:layout/>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -7653,7 +7672,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-1CEE-450F-85DF-EE616CFE4BCC}"/>
                 </c:ext>
@@ -8071,6 +8092,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -21623,43 +21645,140 @@
       <c r="C77" s="13">
         <v>46098</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-      <c r="AA77" s="4"/>
-      <c r="AB77" s="4"/>
-      <c r="AC77" s="4"/>
-      <c r="AD77" s="4"/>
-      <c r="AE77" s="4"/>
-      <c r="AF77" s="4"/>
-      <c r="AG77" s="4"/>
-      <c r="AH77" s="4"/>
-      <c r="AI77" s="4"/>
-      <c r="AJ77" s="4"/>
-      <c r="AK77" s="4"/>
-      <c r="AL77" s="4"/>
-      <c r="AM77" s="4"/>
-      <c r="AN77" s="4"/>
+      <c r="D77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C77,0,"","auto")</f>
+        <v>212.57989501953125</v>
+      </c>
+      <c r="E77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C77,0,"","auto")</f>
+        <v>489.2586669921875</v>
+      </c>
+      <c r="F77" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C77,0,"","auto")</f>
+        <v>500432.90625</v>
+      </c>
+      <c r="G77" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C77,0,"","auto")</f>
+        <v>435669.5625</v>
+      </c>
+      <c r="H77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C77,0,"","auto")</f>
+        <v>44.190132141113281</v>
+      </c>
+      <c r="I77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C77,0,"","auto")</f>
+        <v>51.219924926757813</v>
+      </c>
+      <c r="J77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C77,0,"","auto")</f>
+        <v>57765.4453125</v>
+      </c>
+      <c r="K77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C77,0,"","auto")</f>
+        <v>154100.28125</v>
+      </c>
+      <c r="L77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C77,0,"","auto")</f>
+        <v>1277.49169921875</v>
+      </c>
+      <c r="M77" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C77,0,"","auto")</f>
+        <v>2534.961181640625</v>
+      </c>
+      <c r="N77" s="8">
+        <f t="shared" ref="N77" si="93">(J77+F77-F76)/(D77*H77/100)/1000</f>
+        <v>0.70423481809708932</v>
+      </c>
+      <c r="O77" s="8">
+        <f t="shared" ref="O77" si="94">(K77+G77-G76)/(E77*I77/100)/1000</f>
+        <v>0.70423905509700979</v>
+      </c>
+      <c r="P77" s="8">
+        <f t="shared" ref="P77" si="95">((J77+K77)+F77+G77-F76-G76)/(D77*H77/100+E77*I77/100)/1000</f>
+        <v>0.70423789986357255</v>
+      </c>
+      <c r="Q77" s="8">
+        <f t="shared" ref="Q77" si="96">P77*H77*10</f>
+        <v>311.20365853751372</v>
+      </c>
+      <c r="R77" s="8">
+        <f t="shared" ref="R77" si="97">P77*I77*10</f>
+        <v>360.71012361589771</v>
+      </c>
+      <c r="S77" s="4">
+        <f t="shared" ref="S77" si="98">((J77+K77)+F77+G77-F76-G76)/(D77+E77)</f>
+        <v>345.71510949329775</v>
+      </c>
+      <c r="T77" s="5">
+        <f t="shared" ref="T77" si="99">IF(AL77&lt;3000,0,AL77)</f>
+        <v>91428.8125</v>
+      </c>
+      <c r="U77" s="5">
+        <f t="shared" ref="U77" si="100">IF(AM77&lt;3000,0,AM77)</f>
+        <v>120879.8203125</v>
+      </c>
+      <c r="V77" s="5">
+        <f t="shared" ref="V77" si="101">IF(AN77&lt;3000,0,AN77)</f>
+        <v>0</v>
+      </c>
+      <c r="W77" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X77" s="7">
+        <f t="shared" ref="X77" si="102">J77+K77</f>
+        <v>211865.7265625</v>
+      </c>
+      <c r="Y77" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z77" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA77" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB77" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC77" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD77" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE77" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF77" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG77" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH77" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL77" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C77,0,"","auto")</f>
+        <v>91428.8125</v>
+      </c>
+      <c r="AM77" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C77,0,"","auto")</f>
+        <v>120879.8203125</v>
+      </c>
+      <c r="AN77" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C77,0,"","auto")</f>
+        <v>-421.98843383789063</v>
+      </c>
     </row>
     <row r="78" spans="2:40">
       <c r="B78" s="20">
@@ -21668,43 +21787,140 @@
       <c r="C78" s="13">
         <v>46099</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4"/>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4"/>
-      <c r="Y78" s="4"/>
-      <c r="Z78" s="4"/>
-      <c r="AA78" s="4"/>
-      <c r="AB78" s="4"/>
-      <c r="AC78" s="4"/>
-      <c r="AD78" s="4"/>
-      <c r="AE78" s="4"/>
-      <c r="AF78" s="4"/>
-      <c r="AG78" s="4"/>
-      <c r="AH78" s="4"/>
-      <c r="AI78" s="4"/>
-      <c r="AJ78" s="4"/>
-      <c r="AK78" s="4"/>
-      <c r="AL78" s="4"/>
-      <c r="AM78" s="4"/>
-      <c r="AN78" s="4"/>
+      <c r="D78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C78,0,"","auto")</f>
+        <v>212.42340087890625</v>
+      </c>
+      <c r="E78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C78,0,"","auto")</f>
+        <v>487.30960083007813</v>
+      </c>
+      <c r="F78" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C78,0,"","auto")</f>
+        <v>508913.90625</v>
+      </c>
+      <c r="G78" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C78,0,"","auto")</f>
+        <v>458075.03125</v>
+      </c>
+      <c r="H78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C78,0,"","auto")</f>
+        <v>44.380092620849609</v>
+      </c>
+      <c r="I78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C78,0,"","auto")</f>
+        <v>51.109710693359375</v>
+      </c>
+      <c r="J78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C78,0,"","auto")</f>
+        <v>49778.5390625</v>
+      </c>
+      <c r="K78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C78,0,"","auto")</f>
+        <v>131511.96875</v>
+      </c>
+      <c r="L78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C78,0,"","auto")</f>
+        <v>833.96905517578125</v>
+      </c>
+      <c r="M78" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C78,0,"","auto")</f>
+        <v>2436.007080078125</v>
+      </c>
+      <c r="N78" s="8">
+        <f t="shared" ref="N78:N79" si="103">(J78+F78-F77)/(D78*H78/100)/1000</f>
+        <v>0.61798293469369792</v>
+      </c>
+      <c r="O78" s="8">
+        <f t="shared" ref="O78:O79" si="104">(K78+G78-G77)/(E78*I78/100)/1000</f>
+        <v>0.61798713460374488</v>
+      </c>
+      <c r="P78" s="8">
+        <f t="shared" ref="P78:P79" si="105">((J78+K78)+F78+G78-F77-G77)/(D78*H78/100+E78*I78/100)/1000</f>
+        <v>0.61798598138705885</v>
+      </c>
+      <c r="Q78" s="8">
+        <f t="shared" ref="Q78:Q79" si="106">P78*H78*10</f>
+        <v>274.26275092344315</v>
+      </c>
+      <c r="R78" s="8">
+        <f t="shared" ref="R78:R79" si="107">P78*I78*10</f>
+        <v>315.85084721244351</v>
+      </c>
+      <c r="S78" s="4">
+        <f t="shared" ref="S78:S79" si="108">((J78+K78)+F78+G78-F77-G77)/(D78+E78)</f>
+        <v>303.22562469440794</v>
+      </c>
+      <c r="T78" s="5">
+        <f t="shared" ref="T78:T79" si="109">IF(AL78&lt;3000,0,AL78)</f>
+        <v>75146</v>
+      </c>
+      <c r="U78" s="5">
+        <f t="shared" ref="U78:U79" si="110">IF(AM78&lt;3000,0,AM78)</f>
+        <v>105539</v>
+      </c>
+      <c r="V78" s="5">
+        <f t="shared" ref="V78:V79" si="111">IF(AN78&lt;3000,0,AN78)</f>
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X78" s="7">
+        <f t="shared" ref="X78:X79" si="112">J78+K78</f>
+        <v>181290.5078125</v>
+      </c>
+      <c r="Y78" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z78" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA78" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB78" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC78" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD78" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE78" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF78" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG78" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH78" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL78" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C78,0,"","auto")</f>
+        <v>75146</v>
+      </c>
+      <c r="AM78" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C78,0,"","auto")</f>
+        <v>105539</v>
+      </c>
+      <c r="AN78" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C78,0,"","auto")</f>
+        <v>578</v>
+      </c>
     </row>
     <row r="79" spans="2:40">
       <c r="B79" s="20">
@@ -21713,43 +21929,140 @@
       <c r="C79" s="13">
         <v>46100</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4"/>
-      <c r="W79" s="4"/>
-      <c r="X79" s="4"/>
-      <c r="Y79" s="4"/>
-      <c r="Z79" s="4"/>
-      <c r="AA79" s="4"/>
-      <c r="AB79" s="4"/>
-      <c r="AC79" s="4"/>
-      <c r="AD79" s="4"/>
-      <c r="AE79" s="4"/>
-      <c r="AF79" s="4"/>
-      <c r="AG79" s="4"/>
-      <c r="AH79" s="4"/>
-      <c r="AI79" s="4"/>
-      <c r="AJ79" s="4"/>
-      <c r="AK79" s="4"/>
-      <c r="AL79" s="4"/>
-      <c r="AM79" s="4"/>
-      <c r="AN79" s="4"/>
+      <c r="D79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$1,Sheet1!C79,0,"","auto")</f>
+        <v>202.94000244140625</v>
+      </c>
+      <c r="E79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$2,Sheet1!C79,0,"","auto")</f>
+        <v>486.739990234375</v>
+      </c>
+      <c r="F79" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$3,Sheet1!C79,0,"","auto")</f>
+        <v>507353</v>
+      </c>
+      <c r="G79" s="7">
+        <f>_xll.PIArcVal(Sheet1!$A$4,Sheet1!C79,0,"","auto")</f>
+        <v>453811</v>
+      </c>
+      <c r="H79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$5,Sheet1!C79,0,"","auto")</f>
+        <v>44.509998321533203</v>
+      </c>
+      <c r="I79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$6,Sheet1!C79,0,"","auto")</f>
+        <v>50.689998626708984</v>
+      </c>
+      <c r="J79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$7,Sheet1!C79,0,"","auto")</f>
+        <v>59191</v>
+      </c>
+      <c r="K79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$8,Sheet1!C79,0,"","auto")</f>
+        <v>161677</v>
+      </c>
+      <c r="L79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$9,Sheet1!C79,0,"","auto")</f>
+        <v>1077.300048828125</v>
+      </c>
+      <c r="M79" s="6">
+        <f>_xll.PIArcVal(Sheet1!$A$10,Sheet1!C79,0,"","auto")</f>
+        <v>2719.590087890625</v>
+      </c>
+      <c r="N79" s="8">
+        <f t="shared" si="103"/>
+        <v>0.63800500680795724</v>
+      </c>
+      <c r="O79" s="8">
+        <f t="shared" si="104"/>
+        <v>0.63800076742187628</v>
+      </c>
+      <c r="P79" s="8">
+        <f t="shared" si="105"/>
+        <v>0.63800190354329345</v>
+      </c>
+      <c r="Q79" s="8">
+        <f t="shared" si="106"/>
+        <v>283.9746365584698</v>
+      </c>
+      <c r="R79" s="8">
+        <f t="shared" si="107"/>
+        <v>323.40315614447263</v>
+      </c>
+      <c r="S79" s="4">
+        <f t="shared" si="108"/>
+        <v>311.80121909247816</v>
+      </c>
+      <c r="T79" s="5">
+        <f t="shared" si="109"/>
+        <v>75146</v>
+      </c>
+      <c r="U79" s="5">
+        <f t="shared" si="110"/>
+        <v>105539</v>
+      </c>
+      <c r="V79" s="5">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="W79" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X79" s="7">
+        <f t="shared" si="112"/>
+        <v>220868</v>
+      </c>
+      <c r="Y79" s="4">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="Z79" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="AA79" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="AB79" s="9">
+        <v>264.32</v>
+      </c>
+      <c r="AC79" s="9">
+        <v>323.33999999999997</v>
+      </c>
+      <c r="AD79" s="4">
+        <v>44.27</v>
+      </c>
+      <c r="AE79" s="4">
+        <v>52.51</v>
+      </c>
+      <c r="AF79" s="9">
+        <v>1072</v>
+      </c>
+      <c r="AG79" s="9">
+        <v>830</v>
+      </c>
+      <c r="AH79" s="4">
+        <v>252143</v>
+      </c>
+      <c r="AI79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="4">
+        <v>210000</v>
+      </c>
+      <c r="AL79" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$11,Sheet1!C79,0,"","auto")</f>
+        <v>75146</v>
+      </c>
+      <c r="AM79" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$12,Sheet1!C79,0,"","auto")</f>
+        <v>105539</v>
+      </c>
+      <c r="AN79" s="5">
+        <f>_xll.PIArcVal(Sheet1!$A$13,Sheet1!C79,0,"","auto")</f>
+        <v>578</v>
+      </c>
     </row>
     <row r="80" spans="2:40">
       <c r="B80" s="20">
